--- a/data/kalo_cj/picking_sheet_2026-10-29.xlsx
+++ b/data/kalo_cj/picking_sheet_2026-10-29.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Picking sheet'!$A$1:$AG$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Picking sheet'!$A$1:$AI$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG51"/>
+  <dimension ref="A1:AI51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,11 +446,11 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
@@ -466,8 +466,10 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="40" customWidth="1" min="32" max="32"/>
-    <col width="50" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="40" customWidth="1" min="34" max="34"/>
+    <col width="50" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -528,110 +530,120 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>photo_verdict</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>photo_note</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>cj_name</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>cj_sku</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>cj_url</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>cj_cost</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>cj_weight_g</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ship_from</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>cj_ship</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ship_method</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ship_days</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>landed</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>kept_per_order</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>breakeven_cpa</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>price_for_10</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>vs_tiktok_pct</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>sizes_ok</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>cj_listed</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>cj_stock</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>cj_us_stock</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>cj_reviews</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>cj_avg_rating</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>review_note</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -687,74 +699,84 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Same chunky lug-sole penny loafer shape in black and brown; CJ has a metal bit instead of the croc-embossed strap.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Women Classic Elegant Fashion 2026 New Round Toe Block Low Heel Loafer Leather Shoes Elegant Versatile Pumps</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>CJNS3043308</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/women-classic-elegant-fashion-2026-new-round-toe-block-low-heel-loafer-leather-shoes-elegant-versatile-pumps-p-2085598370886311938.html</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>6.6</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>500</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>11.32</v>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>17.92</v>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="X2" s="2" t="n">
         <v>22.23</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>42.23</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>52.99</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AA2" t="n">
         <v>-19</v>
       </c>
-      <c r="Z2" t="b">
+      <c r="AB2" t="b">
         <v>1</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>5</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AD2" t="n">
         <v>103466</v>
       </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>Generic round-toe low block-heel loafer in black/brown PU, unbranded lookalike of the Clarks heeled loafer (no Clarks leather or cushioning); low listedNum (5).</t>
         </is>
@@ -810,74 +832,84 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Same high-waist satin wide-leg pant; CJ photo is pink but black is a variant. Fabric is acetate satin.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Casual Pants High Waist Acetate Satin Wide Leg Pants For Women</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>CJTZ1911661</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/casual-pants-high-waist-acetate-satin-wide-leg-pants-for-women-p-1731134489503469568.html</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>380</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>9.5</v>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>18.95</v>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="X3" s="2" t="n">
         <v>17.26</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>37.26</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>53.99</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>-12</v>
       </c>
-      <c r="Z3" t="b">
+      <c r="AB3" t="b">
         <v>1</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>78</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AD3" t="n">
         <v>191156</v>
       </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>High-waist acetate-look satin wide-leg pants in apricot/pink/black/gray; Kalodata title gives no detail, so exact cut and waistband may differ.</t>
         </is>
@@ -933,74 +965,84 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Winner is a bold thick oval cat-eye; CJ is a thin half-rim mini cat-eye. Different look.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Cat Eye Sunglasses Women European And American Fashion Trending</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>CJCF1968233</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/cat-eye-sunglasses-women-european-and-american-fashion-trending-p-1757567002828349440.html</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>1.65</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>40</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>5.27</v>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>6.92</v>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="X4" s="2" t="n">
         <v>14.61</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>34.61</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>40.99</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>-10</v>
       </c>
-      <c r="Z4" t="b">
+      <c r="AB4" t="b">
         <v>1</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
         <v>357</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AD4" t="n">
         <v>111129</v>
       </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>Generic plastic-frame trendy cat-eye sunglasses in 9 colourways; frame thickness vs the bold Astra and the UV rating are not stated on the listing.</t>
         </is>
@@ -1056,74 +1098,84 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Same eye-mask hood idea (the TikTok hook); CJ is a pullover not a zip-up and has no mega-fit claim.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Eye-mask Hoodie 350g Fleece-lined Sweatshirt</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>CJWY2725041</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/eye-mask-hoodie-350g-fleece-lined-sweatshirt-p-2601110708231630100.html</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>13.43</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>410</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>23.38</v>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="X5" s="2" t="n">
         <v>13.94</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>33.94</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>58.99</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>-6</v>
       </c>
-      <c r="Z5" t="b">
+      <c r="AB5" t="b">
         <v>1</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>10</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AD5" t="n">
         <v>119616</v>
       </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>Fleece-lined hoodie with built-in eye-mask hood (same travel angle) in 4 colours; pullover not zip-up, no silk-lined hood, men's/unisex cut.</t>
         </is>
@@ -1179,71 +1231,81 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Winner is an all-fur slipper; CJ is a perforated garden clog with a fur cuff.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Fuzzy Plush Garden Clogs Mules Slippers Home Indoor Couple Slippers</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>CJNS1050784</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/fuzzy-plush-garden-clogs-mules-slippers-home-indoor-couple-slippers-p-1373889976009363456.html</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>2.3</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>269</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>7.81</v>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>10.11</v>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="X6" s="2" t="n">
         <v>13.8</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>33.8</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>43.99</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>-8</v>
       </c>
-      <c r="Z6" t="b">
+      <c r="AB6" t="b">
         <v>1</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>543</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AD6" t="n">
         <v>2000000</v>
       </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>Unbranded plush-lined garden clog mule (closed toe, fuzzy lining) rather than Crocs Cozzzy open sandal-slipper; listed as men's/couple sizes 36-45.</t>
         </is>
@@ -1299,71 +1361,81 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Winner is a fur-covered clog; CJ is a perforated garden clog with a fur cuff.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Fuzzy Plush Garden Clogs Mules Slippers Home Indoor Couple Slippers</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>CJNS1050784</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/fuzzy-plush-garden-clogs-mules-slippers-home-indoor-couple-slippers-p-1373889976009363456.html</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>2.3</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>269</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>7.81</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>10.11</v>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="X7" s="2" t="n">
         <v>13.56</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>33.56</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>43.99</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>-8</v>
       </c>
-      <c r="Z7" t="b">
+      <c r="AB7" t="b">
         <v>1</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AC7" t="n">
         <v>543</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AD7" t="n">
         <v>2000000</v>
       </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>Same CJ product as S01: unbranded EVA garden clog with plush lining; lacks the Crocs furry exterior and strap; no closer furry-lined clog found on CJ.</t>
         </is>
@@ -1419,74 +1491,84 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Barbed-wire idea matches but CJ is a chunky silver iced-out chain; the winner is a dainty gold choker. CJ cost $26.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>2.5mm Wire Chain Hip Hop Necklace Micro Inlaid Sun Word Buckle Thorns</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>CJLX1518256</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/2.5mm-wire-chain-hip-hop-necklace-micro-inlaid-sun-word-buckle-thorns-p-1544546445079498752.html</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>26.41</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>42</v>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>5.01</v>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>CJPacket Pure Electricity</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>7-14</t>
         </is>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>31.42</v>
       </c>
-      <c r="V8" s="2" t="n">
+      <c r="X8" s="2" t="n">
         <v>13.04</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>33.04</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>67.99000000000001</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>-3</v>
       </c>
-      <c r="Z8" t="b">
+      <c r="AB8" t="b">
         <v>1</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>14</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
         <v>192925</v>
       </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>Unbranded lookalike: thin 2.5mm micro-pave CZ barbed-wire chain on gold-plated copper (gold/white gold, 14-20in), not the Danielle Guizio x M Jewelers piece; cost is high for CJ.</t>
         </is>
@@ -1542,74 +1624,84 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Winner is a draped boat-neck cowl gown with slit; CJ is a square-neck strappy mermaid chiffon gown.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>Square Neck Ruched Waist Sleeveless Maxi Evening Dress</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>CJLY2902281</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/square-neck-ruched-waist-sleeveless-maxi-evening-dress-p-2058739052119445505.html</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>12.99</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>530</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>11.78</v>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>24.77</v>
       </c>
-      <c r="V9" s="2" t="n">
+      <c r="X9" s="2" t="n">
         <v>10.05</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>30.05</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
         <v>59.99</v>
       </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="b">
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="b">
         <v>1</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AC9" t="n">
         <v>21</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AD9" t="n">
         <v>485413</v>
       </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
         <is>
           <t>Sleeveless ruched-waist maxi evening dress in 8 colours; square neck instead of convertible cowl/scoop neck, and not stated as knit.</t>
         </is>
@@ -1665,74 +1757,84 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Winner is a full-zip big-hood hoodie with script embroidery; CJ is a half-zip pullover with rope drawstrings.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>INAWLY Split Collar Zip-Up Hoodie Sweatshirt</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>CJWY2423586</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/inawly-split-collar-zip-up-hoodie-sweatshirt-p-1942114697997361154.html</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>4.58</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>400</v>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>8.539999999999999</v>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>UniUni+</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>3-8</t>
         </is>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>13.12</v>
       </c>
-      <c r="V10" s="2" t="n">
+      <c r="X10" s="2" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>29.2</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
         <v>47.99</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>4</v>
       </c>
-      <c r="Z10" t="b">
+      <c r="AB10" t="b">
         <v>1</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AC10" t="n">
         <v>43</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AD10" t="n">
         <v>294115</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
         <v>283</v>
       </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>Women's split/high-collar full-zip hoodie in solid colours; lacks FDR's embroidered script, washed finish and oversized hood (CN ship option: LuWei Ordinary $9.80, 5-11 days).</t>
         </is>
@@ -1788,79 +1890,89 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Winner is a strapped clog on a white platform sole; CJ is a suede penny mule on a cork sole. CJ box shows another brand's logo: avoid.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>Cowhide Retro Closed Toe Half Slippers Mule Platform Casual Shoes Men And Women Same Style</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>CJYD2567515</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/cowhide-retro-closed-toe-half-slippers-mule-platform-casual-shoes-men-and-women-same-style-p-2510230719111608200.html</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>21.47</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>840</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>15.56</v>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>37.03</v>
       </c>
-      <c r="V11" s="2" t="n">
+      <c r="X11" s="2" t="n">
         <v>9.119999999999999</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>29.12</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>73.99000000000001</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>3</v>
       </c>
-      <c r="Z11" t="b">
+      <c r="AB11" t="b">
         <v>1</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AC11" t="n">
         <v>11</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AD11" t="n">
         <v>295229</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>1</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
         <v>5</v>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>Good value, matches photos; runs small, size up.</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t>Unbranded closed-toe backless suede/leather platform mule clog (Boston-style) vs HEYDUDE fabric Austin Lift; unisex, heavy at 840 g.</t>
         </is>
@@ -1916,74 +2028,84 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Winner is big marquise crystal bezel studs; CJ is tiny emerald baguettes with a pearl drop.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>925 Sterling Silver 14k Gold Plated French Emerald Stud Earrings</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>CJLX1504011</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/925-sterling-silver-14k-gold-plated-french-emerald-stud-earrings-p-1537334939690217472.html</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>3.45</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>12</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>4.48</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>CJPacket Postal</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>5-9</t>
         </is>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>7.93</v>
       </c>
-      <c r="V12" s="2" t="n">
+      <c r="X12" s="2" t="n">
         <v>5.33</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>25.33</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Z12" t="n">
         <v>41.99</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
         <v>15</v>
       </c>
-      <c r="Z12" t="b">
+      <c r="AB12" t="b">
         <v>1</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AC12" t="n">
         <v>9</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AD12" t="n">
         <v>134738</v>
       </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
         <is>
           <t>14K gold-plated 925 silver studs with emerald-green stones, but the variants are a stick, pearl or asymmetric design, not tiny round clear/emerald CZ mini studs; low listedNum (9).</t>
         </is>
@@ -2039,74 +2161,84 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Plain oversized hoodie; works for a basic hoodie ad but lacks Comfrt's textured fabric and branding look.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>Fashion Solid Color Pullover Hoodie Sweater</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>CJWY1366882</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/fashion-solid-color-pullover-hoodie-sweater-p-1465498406276435968.html</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>6.69</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>510</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>11.48</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U13" t="n">
+      <c r="W13" t="n">
         <v>18.17</v>
       </c>
-      <c r="V13" s="2" t="n">
+      <c r="X13" s="2" t="n">
         <v>4.68</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Y13" t="n">
         <v>24.68</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Z13" t="n">
         <v>52.99</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AA13" t="n">
         <v>13</v>
       </c>
-      <c r="Z13" t="b">
+      <c r="AB13" t="b">
         <v>1</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AC13" t="n">
         <v>40</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
         <v>2009897</v>
       </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
         <is>
           <t>Plain solid pullover hoodie in 8 colours (S-2XL); regular cut and lighter fabric, not a mega-oversized premium fleece.</t>
         </is>
@@ -2162,74 +2294,79 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>INAWLY Split Collar Zip-Up Hoodie Sweatshirt</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>CJWY2423586</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/inawly-split-collar-zip-up-hoodie-sweatshirt-p-1942114697997361154.html</t>
         </is>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>4.58</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>400</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>8.539999999999999</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>UniUni+</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>3-8</t>
         </is>
       </c>
-      <c r="U14" t="n">
+      <c r="W14" t="n">
         <v>13.12</v>
       </c>
-      <c r="V14" s="2" t="n">
+      <c r="X14" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>21.9</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
         <v>47.99</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>25</v>
       </c>
-      <c r="Z14" t="b">
+      <c r="AB14" t="b">
         <v>1</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>43</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
         <v>294115</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AE14" t="n">
         <v>283</v>
       </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
         <is>
           <t>Same CJ product as C18 (no closer high-neck full-zip on CJ): women's split-collar zip-up hoodie, lighter than FDR's heavyweight, no embroidery or oversized hood, women's sizing only (CN ship option: LuWei Ordinary $9.80, 5-11 days).</t>
         </is>
@@ -2285,74 +2422,79 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>Pofash Solid Long Sleeves Autumn Outfits Women Zip Up Hoodie</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>CJLY1235532</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/pofash-solid-long-sleeves-autumn-outfits-women-zip-up-hoodie-p-1421724669576351744.html</t>
         </is>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>8.130000000000001</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>670</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>13.91</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U15" t="n">
+      <c r="W15" t="n">
         <v>22.04</v>
       </c>
-      <c r="V15" s="2" t="n">
+      <c r="X15" s="2" t="n">
         <v>0.71</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Y15" t="n">
         <v>20.71</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Z15" t="n">
         <v>56.99</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AA15" t="n">
         <v>22</v>
       </c>
-      <c r="Z15" t="b">
+      <c r="AB15" t="b">
         <v>1</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AC15" t="n">
         <v>144</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AD15" t="n">
         <v>717762</v>
       </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
         <is>
           <t>Solid women's full-zip hoodie in pink/black/brown/khaki; regular women's cut rather than mega-oversized unisex cloud-soft fleece.</t>
         </is>
@@ -2408,71 +2550,76 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>Women Square Toe Platform Block Heel Knee High Boots</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>CJNS3087809</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/women-square-toe-platform-block-heel-knee-high-boots-p-2091462800921911297.html</t>
         </is>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>10</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>500</v>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>11.32</v>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>21.32</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="X16" s="3" t="n">
         <v>-0.8</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>19.2</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Z16" t="n">
         <v>56.99</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AA16" t="n">
         <v>29</v>
       </c>
-      <c r="Z16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="AB16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
         <v>31</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AD16" t="n">
         <v>41731</v>
       </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
         <is>
           <t>PU square-toe platform block-heel knee-high boot; only Wine Red, sizes EU 36-40, side zipper not stated; flat 500 g listed weight looks too low for knee-high platform boots.</t>
         </is>
@@ -2528,74 +2675,79 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>Slim-fit Solid Color One-shoulder Pleated Split Satin Dress</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>CJLY2081470</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/slim-fit-solid-color-one-shoulder-pleated-split-satin-dress-p-2407120158221601900.html</t>
         </is>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>12.94</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>373</v>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>9.390000000000001</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U17" t="n">
+      <c r="W17" t="n">
         <v>22.33</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="X17" s="3" t="n">
         <v>-1.35</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Y17" t="n">
         <v>18.65</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Z17" t="n">
         <v>57.99</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
         <v>29</v>
       </c>
-      <c r="Z17" t="b">
+      <c r="AB17" t="b">
         <v>1</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AC17" t="n">
         <v>127</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AD17" t="n">
         <v>664700</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
         <is>
           <t>One-shoulder slim satin long dress with high split in 12 colours; adds pleating detail, otherwise same style (polyester satin).</t>
         </is>
@@ -2651,82 +2803,87 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>Solid color loose solid color pullover hoodie</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>CJNSWTWY04562</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/solid-color-loose-solid-color-pullover-hoodie-p-51FE7A58-61B7-4261-AA56-E9E090525B3A.html</t>
         </is>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>7.25</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>470</v>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>10.87</v>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>18.12</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="X18" s="3" t="n">
         <v>-2.88</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Y18" t="n">
         <v>17.12</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Z18" t="n">
         <v>52.99</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
         <v>37</v>
       </c>
-      <c r="Z18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
         <v>16</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AD18" t="n">
         <v>300000</v>
       </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
         <v>20</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AG18" t="n">
         <v>4.25</v>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AH18" t="inlineStr">
         <is>
           <t>Good material and quality; many say it runs 1-2 sizes small.</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>Solid pullover hoodie with kangaroo pocket in grey/dark grey/black, sizes M-3XL (men's category); listed as loose but reviews say it runs small, not mega-oversized.</t>
         </is>
@@ -2782,74 +2939,79 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>American Gray Sweatpants For Women Spring &amp; Fall 2025 New High-Waisted Straight-Leg Loose Casual Sweatpants Workwear Wide-Leg Pants</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>CJKT3082324</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/american-gray-sweatpants-for-women-spring-fall-2025-new-high-waisted-straight-leg-loose-casual-sweatpants-workwear-wide-leg-pants-p-2090985687352066049.html</t>
         </is>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>9.43</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>400</v>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U19" t="n">
+      <c r="W19" t="n">
         <v>19.23</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="X19" s="3" t="n">
         <v>-4.85</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Y19" t="n">
         <v>15.15</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Z19" t="n">
         <v>53.99</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AA19" t="n">
         <v>43</v>
       </c>
-      <c r="Z19" t="b">
+      <c r="AB19" t="b">
         <v>1</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
         <v>11</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AD19" t="n">
         <v>75696</v>
       </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
         <is>
           <t>Women's high-waist loose straight-leg sweatpants in grey/black only; budget fabric vs Comfrt's elevated soft loungewear, and not unisex.</t>
         </is>
@@ -2905,74 +3067,79 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>Women's High-rise Stretch Slim Wide-leg Jeans</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>CJNZ1390315</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/womens-high-rise-stretch-slim-wide-leg-jeans-p-1476131678610132992.html</t>
         </is>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>5.89</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>880</v>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>16.17</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U20" t="n">
+      <c r="W20" t="n">
         <v>22.06</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="X20" s="3" t="n">
         <v>-5.23</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Y20" t="n">
         <v>14.77</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Z20" t="n">
         <v>56.99</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
         <v>41</v>
       </c>
-      <c r="Z20" t="b">
+      <c r="AB20" t="b">
         <v>1</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>46</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>324756</v>
       </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
         <is>
           <t>Stretch slim-fit wide-leg (slight flare) jeans in light blue only; high-rise not mid-rise, no raw hem or tummy-control claim, waist sizes 26-32.</t>
         </is>
@@ -3028,74 +3195,79 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>Curlers Curling Rod Ribbon Headband Silk Hair Rollers DIY Hairstyle Tools For Women</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>CJTF1360098</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/curlers-curling-rod-ribbon-headband-silk-hair-rollers-diy-hairstyle-tools-for-women-p-1462980936332349440.html</t>
         </is>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>2.35</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>116</v>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>5.96</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U21" t="n">
+      <c r="W21" t="n">
         <v>8.31</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="X21" s="3" t="n">
         <v>-8.06</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Y21" t="n">
         <v>11.94</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Z21" t="n">
         <v>41.99</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AA21" t="n">
         <v>88</v>
       </c>
-      <c r="Z21" t="b">
+      <c r="AB21" t="b">
         <v>1</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AC21" t="n">
         <v>694</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AD21" t="n">
         <v>360968</v>
       </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
         <is>
           <t>Unbranded heatless curling rod headband in fiber-cotton (brown/pink/blue/black, short/long), not heather-gray athletic jersey; Chinese listing name hints it may be an octopus-style multi-arm curler, so check photos.</t>
         </is>
@@ -3151,74 +3323,79 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
           <t>Irish Celtic Knot Pendant Necklace</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>CJLX2076022</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/irish-celtic-knot-pendant-necklace-p-2407050613261611900.html</t>
         </is>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>0.76</v>
       </c>
-      <c r="P22" t="n">
+      <c r="R22" t="n">
         <v>16</v>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>4.6</v>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>CJPacket Postal</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>5-9</t>
         </is>
       </c>
-      <c r="U22" t="n">
+      <c r="W22" t="n">
         <v>5.36</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="X22" s="3" t="n">
         <v>-8.17</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>11.83</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Z22" t="n">
         <v>38.99</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>105</v>
       </c>
-      <c r="Z22" t="b">
+      <c r="AB22" t="b">
         <v>1</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>200</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AD22" t="n">
         <v>11597</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
         <is>
           <t>Alloy Irish Celtic knot pendant with one blue imitation-opal centre stone, not a silver-plated copper triquetra with a choice of 12 birthstone crystals; no birthstone/gift-for-mom angle.</t>
         </is>
@@ -3274,74 +3451,79 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
           <t>Zip-up Pullover Knit Sweater For Women</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>CJMY3191798</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/zip-up-pullover-knit-sweater-for-women-p-2609240114181624600.html</t>
         </is>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>7.99</v>
       </c>
-      <c r="P23" t="n">
+      <c r="R23" t="n">
         <v>590</v>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>12.69</v>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U23" t="n">
+      <c r="W23" t="n">
         <v>20.68</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="X23" s="3" t="n">
         <v>-8.59</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Y23" t="n">
         <v>11.41</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Z23" t="n">
         <v>55.99</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>59</v>
       </c>
-      <c r="Z23" t="b">
+      <c r="AB23" t="b">
         <v>1</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>7</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>343139</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
         <is>
           <t>Women's loose zip-neck knit pullover in 6 colours, XS-4XL; acrylic, no stated collar/V-neck rib detail or thumbholes, and only 7 listings (new item).</t>
         </is>
@@ -3397,74 +3579,79 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>Nude Patent Leather Pointed Toe Slingback High Heels, Red Bottom Stiletto Pumps With Cutout Detail, Elegant Dress Shoes For Women</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>CJNS2898869</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/nude-patent-leather-pointed-toe-slingback-high-heels-red-bottom-stiletto-pumps-with-cutout-detail-elegant-dress-shoes-for-women-p-2057351758316924930.html</t>
         </is>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>8.06</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>500</v>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>11.32</v>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>19.38</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="X24" s="3" t="n">
         <v>-9.32</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Y24" t="n">
         <v>10.68</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Z24" t="n">
         <v>53.99</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AA24" t="n">
         <v>64</v>
       </c>
-      <c r="Z24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="AB24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
         <v>30</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
         <v>64277</v>
       </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
         <is>
           <t>Same pointed-toe patent slingback stiletto with cutout sides, but has a red-bottom sole and listing variants show only White (title says Nude), EU 36-40.</t>
         </is>
@@ -3520,71 +3707,76 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>Basic Fitted Sleeveless Tank Top For Women</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>CJCS2953816</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/basic-fitted-sleeveless-tank-top-for-women-p-2606250338301603300.html</t>
         </is>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>3.01</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>260</v>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>7.68</v>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U25" t="n">
+      <c r="W25" t="n">
         <v>10.69</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="X25" s="3" t="n">
         <v>-9.56</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
         <v>10.44</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>44.99</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AA25" t="n">
         <v>93</v>
       </c>
-      <c r="Z25" t="b">
+      <c r="AB25" t="b">
         <v>1</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AC25" t="n">
         <v>23</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
         <v>250008</v>
       </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
         <is>
           <t>Generic fitted sleeveless basic tank in 7 neutral colours S-2XL; Kalodata title gives no detail, so fabric, neckline and naom's exact cut are unverified.</t>
         </is>
@@ -3640,71 +3832,76 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
           <t>New Cross-Border Washed Denim Shirt Jacket For Women, Frayed Hem Denim Jacket</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>CJWO3098032</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/new-cross-border-washed-denim-shirt-jacket-for-women-european-and-american-style-autumn-and-winter-personalized-street-style-with-frayed-hem-denim-jacket-p-2092509532383215617.html</t>
         </is>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>11.12</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>500</v>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>11.32</v>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U26" t="n">
+      <c r="W26" t="n">
         <v>22.44</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="X26" s="3" t="n">
         <v>-9.81</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Y26" t="n">
         <v>10.19</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Z26" t="n">
         <v>57.99</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
         <v>62</v>
       </c>
-      <c r="Z26" t="b">
+      <c r="AB26" t="b">
         <v>1</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AC26" t="n">
         <v>9</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>359509</v>
       </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
         <is>
           <t>Washed denim shirt-jacket with frayed hem in light/dark blue plus dyed colours; less oversized and less distressed than EMMIOL's vintage shacket.</t>
         </is>
@@ -3760,74 +3957,79 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>Wide Belt Niche Retro Y2g Hot Girl Suede Frosted Wide-brimmed Belt Silver Buckle</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>CJYD2343800</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/wide-belt-niche-retro-y2g-hot-girl-suede-frosted-wide-brimmed-belt-silver-buckle-p-2504020721441615200.html</t>
         </is>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>1.51</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>175</v>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>6.92</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U27" t="n">
+      <c r="W27" t="n">
         <v>8.43</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="X27" s="3" t="n">
         <v>-10.25</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Y27" t="n">
         <v>9.75</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Z27" t="n">
         <v>42.99</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AA27" t="n">
         <v>114</v>
       </c>
-      <c r="Z27" t="b">
+      <c r="AB27" t="b">
         <v>1</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AC27" t="n">
         <v>16</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>16735</v>
       </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
         <is>
           <t>Wide (&gt;4cm) PU faux-suede belt in brown/black with a silver alloy pin buckle, not a gold buckle; otherwise the same chunky dress-belt look.</t>
         </is>
@@ -3883,74 +4085,79 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
           <t>Wide Leg Jeans For Women Bottom Baggy Denim Pants Trousers</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>CJNZ1345715</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/wide-leg-jeans-for-women-bottom-baggy-denim-pants-trousers-p-1457536173303009280.html</t>
         </is>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>16.16</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>581</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>12.56</v>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U28" t="n">
+      <c r="W28" t="n">
         <v>28.72</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="X28" s="3" t="n">
         <v>-11.3</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Y28" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Z28" t="n">
         <v>64.99000000000001</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
         <v>59</v>
       </c>
-      <c r="Z28" t="b">
+      <c r="AB28" t="b">
         <v>1</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AC28" t="n">
         <v>428</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
         <v>346201</v>
       </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
         <is>
           <t>Generic blue baggy wide-leg denim; no low-rise zipper-pocket asymmetric detailing like the Halara jeans.</t>
         </is>
@@ -4006,74 +4213,79 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
           <t>Women Solid Color Long Sleeve Casual Open Front Knit Cardigan</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>CJJK2425784</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/women-solid-color-long-sleeve-casual-open-front-knit-cardigan-p-1942875414726483970.html</t>
         </is>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>5.48</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>550</v>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>10.14</v>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>UniUni+</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>3-8</t>
         </is>
       </c>
-      <c r="U29" t="n">
+      <c r="W29" t="n">
         <v>15.62</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="X29" s="3" t="n">
         <v>-11.44</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Y29" t="n">
         <v>8.56</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Z29" t="n">
         <v>49.99</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AA29" t="n">
         <v>88</v>
       </c>
-      <c r="Z29" t="b">
+      <c r="AB29" t="b">
         <v>1</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AC29" t="n">
         <v>45</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="n">
         <v>141928</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="n">
         <v>298</v>
       </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
         <is>
           <t>Solid open-front knit cardigan in brown/pink only; plain long sleeves, not the lantern-sleeve oversized cut, and few colours.</t>
         </is>
@@ -4129,74 +4341,79 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
           <t>Retro Anti Blue Ray Computer Glasses Women Round Eye Glass Men Blue Light Blocking Fashion Eyewear Optical Frames</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>CJYJ1203007</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/retro-anti-blue-ray-computer-glasses-women-round-eye-glass-men-blue-light-blocking-fashion-eyewear-optical-frames-p-1412242051956871168.html</t>
         </is>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>1.38</v>
       </c>
-      <c r="P30" t="n">
+      <c r="R30" t="n">
         <v>40</v>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>5.27</v>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>6.65</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="X30" s="3" t="n">
         <v>-11.48</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Y30" t="n">
         <v>8.52</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Z30" t="n">
         <v>40.99</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AA30" t="n">
         <v>144</v>
       </c>
-      <c r="Z30" t="b">
+      <c r="AB30" t="b">
         <v>1</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AC30" t="n">
         <v>127</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
         <v>127222</v>
       </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="inlineStr">
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
         <is>
           <t>Unbranded retro plastic full-frame non-prescription glasses (matte/gloss black, leopard, clear); the English title claims blue-light blocking but the Chinese spec only says plain lens and no UV400, so confirm the lens coating.</t>
         </is>
@@ -4252,71 +4469,76 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
           <t>Pointed Toe Slip-on Pumps Office PU Rubber Sole</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>CJNS3133826</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/pointed-toe-slip-on-pumps-office-pu-rubber-sole-p-2609070130101600600.html</t>
         </is>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>5.76</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>719</v>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>13.72</v>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U31" t="n">
+      <c r="W31" t="n">
         <v>19.48</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="X31" s="3" t="n">
         <v>-11.51</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Y31" t="n">
         <v>8.49</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Z31" t="n">
         <v>54.99</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AA31" t="n">
         <v>79</v>
       </c>
-      <c r="Z31" t="b">
+      <c r="AB31" t="b">
         <v>1</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
         <v>27</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
         <v>212983</v>
       </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
         <is>
           <t>Same PU pointed-toe slip-on stiletto pump with rubber sole (6-8 cm heel); cj_cost_max 52.89 is a pricing anomaly on 3 size-42/43 variants, other sizes cost $5.30-5.76. Cost set to $5.76 (dearest normal size); the $52.89 listed max is 3 EU 42/43 variants only.</t>
         </is>
@@ -4372,74 +4594,79 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>Butt Lifting Workout Leggings For Women Seamless High Waisted Yoga Pants</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>CJDD1671462</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/butt-lifting-workout-leggings-for-women-seamless-high-waisted-yoga-pants-p-1619989245694201856.html</t>
         </is>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>7.96</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>190</v>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>7.16</v>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U32" t="n">
+      <c r="W32" t="n">
         <v>15.12</v>
       </c>
-      <c r="V32" s="3" t="n">
+      <c r="X32" s="3" t="n">
         <v>-12.23</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>7.77</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Z32" t="n">
         <v>49.99</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AA32" t="n">
         <v>99</v>
       </c>
-      <c r="Z32" t="b">
+      <c r="AB32" t="b">
         <v>1</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
         <v>968</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
         <v>495486</v>
       </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="inlineStr">
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
         <is>
           <t>Seamless high-waist butt-lifting yoga leggings in 8 colours; seamless knit rather than buttery-soft brushed fabric, length not 25in-specific.</t>
         </is>
@@ -4495,74 +4722,79 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
           <t>Raw Hem Wide Legs Jeans For Women Baggy Straight Trousers</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>CJNZ1812753</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/raw-hem-wide-legs-jeans-for-women-baggy-straight-trousers-p-1686543273273339904.html</t>
         </is>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>6.73</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>580</v>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>12.54</v>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U33" t="n">
+      <c r="W33" t="n">
         <v>19.27</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="X33" s="3" t="n">
         <v>-12.47</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
         <v>7.53</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Z33" t="n">
         <v>53.99</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AA33" t="n">
         <v>84</v>
       </c>
-      <c r="Z33" t="b">
+      <c r="AB33" t="b">
         <v>1</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AC33" t="n">
         <v>254</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AD33" t="n">
         <v>112166</v>
       </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="inlineStr">
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
         <is>
           <t>Baggy raw-hem wide-leg denim in one wash, waist sizes 26-34; raw hem only (no ripped distressing), no stretch/BBL shaping or multiple inseam lengths.</t>
         </is>
@@ -4618,71 +4850,76 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>Sleeveless Square Neck Corset Mermaid Maxi Dress</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>CJLY2895871</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/sleeveless-square-neck-corset-mermaid-maxi-dress-p-2056615484412178434.html</t>
         </is>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>19.4</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>500</v>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>11.32</v>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U34" t="n">
+      <c r="W34" t="n">
         <v>30.72</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="X34" s="3" t="n">
         <v>-13.84</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Y34" t="n">
         <v>6.16</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Z34" t="n">
         <v>66.99000000000001</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AA34" t="n">
         <v>66</v>
       </c>
-      <c r="Z34" t="b">
+      <c r="AB34" t="b">
         <v>1</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AC34" t="n">
         <v>9</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AD34" t="n">
         <v>205036</v>
       </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="inlineStr">
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
         <is>
           <t>Sleeveless square-neck boned-corset jacquard-lace mermaid maxi in pink/blue/black; no floral embroidery, ruching or high slit confirmed.</t>
         </is>
@@ -4738,74 +4975,79 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>Straight-leg Fleece-lined Sweatpants For Men And Women</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>CJXX3207033</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/straight-leg-fleece-lined-sweatpants-for-men-and-women-p-2609290142211617200.html</t>
         </is>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>4.92</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>620</v>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>13.15</v>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U35" t="n">
+      <c r="W35" t="n">
         <v>18.07</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="X35" s="3" t="n">
         <v>-13.86</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
         <v>6.14</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Z35" t="n">
         <v>52.99</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AA35" t="n">
         <v>99</v>
       </c>
-      <c r="Z35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
+      <c r="AB35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
         <v>11</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AD35" t="n">
         <v>175545</v>
       </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="inlineStr">
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
         <is>
           <t>Unisex straight-leg sweatpants in gray/black (regular or fleece-lined); basic budget fabric, sizes start at M (no S).</t>
         </is>
@@ -4861,74 +5103,79 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t>Women's Flat Double Buckle Sandals</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>CJNS2091040</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/womens-flat-double-buckle-sandals-p-2407230719031606200.html</t>
         </is>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>11.35</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>600</v>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>12.85</v>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U36" t="n">
+      <c r="W36" t="n">
         <v>24.2</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="X36" s="3" t="n">
         <v>-14.17</v>
       </c>
-      <c r="W36" t="n">
+      <c r="Y36" t="n">
         <v>5.83</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Z36" t="n">
         <v>59.99</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AA36" t="n">
         <v>82</v>
       </c>
-      <c r="Z36" t="b">
+      <c r="AB36" t="b">
         <v>1</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AC36" t="n">
         <v>60</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AD36" t="n">
         <v>317933</v>
       </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="inlineStr">
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
         <is>
           <t>Unbranded flat two-buckle-strap slide (Arizona style) in PU upper with TPR sole, not molded EVA/Croslite; beige, black, snake colours.</t>
         </is>
@@ -4984,71 +5231,76 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>Christmas Sleepwear Women Fleece Hooded Bathrobe Plush Long Robe Winter</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>CJSY1570363</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/christmas-sleepwear-women-fleece-hooded-bathrobe-plush-long-robe-winter-p-1573120706865942528.html</t>
         </is>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>10.38</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>1100</v>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>19.52</v>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U37" t="n">
+      <c r="W37" t="n">
         <v>29.9</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="X37" s="3" t="n">
         <v>-14.38</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Y37" t="n">
         <v>5.62</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Z37" t="n">
         <v>65.99000000000001</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AA37" t="n">
         <v>70</v>
       </c>
-      <c r="Z37" t="b">
+      <c r="AB37" t="b">
         <v>1</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AC37" t="n">
         <v>198</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AD37" t="n">
         <v>61691</v>
       </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="inlineStr">
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
         <is>
           <t>Full-length hooded plush fleece robe, but the only colourway is a Christmas checkered print (no solids) and it adds a hood.</t>
         </is>
@@ -5104,74 +5356,79 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
           <t>Gold Sterling Silver CZ Colored Diamonds Everyday Simple Necklace</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>CJLX1565932</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/gold-sterling-silver-cz-colored-diamonds-everyday-simple-necklace-p-1570966954834407424.html</t>
         </is>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>5.42</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>12</v>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>4.48</v>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>CJPacket Postal</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>5-9</t>
         </is>
       </c>
-      <c r="U38" t="n">
+      <c r="W38" t="n">
         <v>9.9</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="X38" s="3" t="n">
         <v>-14.45</v>
       </c>
-      <c r="W38" t="n">
+      <c r="Y38" t="n">
         <v>5.55</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Z38" t="n">
         <v>43.99</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AA38" t="n">
         <v>157</v>
       </c>
-      <c r="Z38" t="b">
+      <c r="AB38" t="b">
         <v>1</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AC38" t="n">
         <v>15</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AD38" t="n">
         <v>11298</v>
       </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="inlineStr">
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
         <is>
           <t>Gold-plated sterling silver dainty clavicle chain with CZ stations, but the CZs are multicolour not clear simulated diamond; single gold variant, low listedNum (15); no clear-CZ station chain found on CJ.</t>
         </is>
@@ -5227,74 +5484,79 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
           <t>Round Zirconia Tennis Clavicle Necklace</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>CJLX2103592</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/round-zirconia-tennis-clavicle-necklace-p-2408061124531600400.html</t>
         </is>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>1.95</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>15</v>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>4.57</v>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>CJPacket Postal</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>5-9</t>
         </is>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>6.52</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="X39" s="3" t="n">
         <v>-14.86</v>
       </c>
-      <c r="W39" t="n">
+      <c r="Y39" t="n">
         <v>5.14</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Z39" t="n">
         <v>39.99</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AA39" t="n">
         <v>208</v>
       </c>
-      <c r="Z39" t="b">
+      <c r="AB39" t="b">
         <v>1</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AC39" t="n">
         <v>42</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AD39" t="n">
         <v>25238</v>
       </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="inlineStr">
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
         <is>
           <t>Same round-CZ tennis choker in gold or steel-silver tone, likely plated steel/alloy rather than 14K-plated brass; adjustability not stated.</t>
         </is>
@@ -5350,74 +5612,79 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
           <t>Loose Short Sleeve Side Slit Casual Sweater For Women</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>CJMY2016904</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/loose-short-sleeve-side-slit-casual-sweater-for-women-p-1782224023129165824.html</t>
         </is>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>4.63</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>350</v>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U40" t="n">
+      <c r="W40" t="n">
         <v>13.67</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="X40" s="3" t="n">
         <v>-14.9</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Y40" t="n">
         <v>5.1</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Z40" t="n">
         <v>47.99</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AA40" t="n">
         <v>132</v>
       </c>
-      <c r="Z40" t="b">
+      <c r="AB40" t="b">
         <v>1</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AC40" t="n">
         <v>46</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AD40" t="n">
         <v>255373</v>
       </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="inlineStr">
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
         <is>
           <t>Loose short-sleeve side-slit knit pullover in 5 colours; V-neck with pockets and polyester rather than round-neck puff-sleeve cotton knit.</t>
         </is>
@@ -5473,74 +5740,79 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
           <t>Vintage S925 Sterling Silver Black Gold Palaiba Glass Stone Flower Ring</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>CJLX1855192</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/vintage-s925-sterling-silver-black-gold-palaiba-glass-stone-flower-ring-p-1705832042337935360.html</t>
         </is>
       </c>
-      <c r="O41" t="n">
+      <c r="Q41" t="n">
         <v>4.82</v>
       </c>
-      <c r="P41" t="n">
+      <c r="R41" t="n">
         <v>16</v>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R41" t="n">
+      <c r="T41" t="n">
         <v>4.6</v>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>CJPacket Postal</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>5-9</t>
         </is>
       </c>
-      <c r="U41" t="n">
+      <c r="W41" t="n">
         <v>9.42</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="X41" s="3" t="n">
         <v>-17.04</v>
       </c>
-      <c r="W41" t="n">
+      <c r="Y41" t="n">
         <v>2.96</v>
       </c>
-      <c r="X41" t="n">
+      <c r="Z41" t="n">
         <v>43.99</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AA41" t="n">
         <v>219</v>
       </c>
-      <c r="Z41" t="b">
+      <c r="AB41" t="b">
         <v>1</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AC41" t="n">
         <v>84</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AD41" t="n">
         <v>75673</v>
       </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="inlineStr">
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
         <is>
           <t>S925 silver vintage flower ring with black-gold finish, but the centre stone is a Paraiba-style glass stone, not black obsidian / black lab diamond; one style, US sizes 5-10.</t>
         </is>
@@ -5596,74 +5868,79 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
           <t>Four-leaf clover bracelet</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>CJZBGJJE00037</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/four-leaf-clover-bracelet-p-D7A0B1A2-0DE4-4CF4-826A-391362A29709.html</t>
         </is>
       </c>
-      <c r="O42" t="n">
+      <c r="Q42" t="n">
         <v>13.89</v>
       </c>
-      <c r="P42" t="n">
+      <c r="R42" t="n">
         <v>20</v>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R42" t="n">
+      <c r="T42" t="n">
         <v>4.73</v>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>CJPacket Postal</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>5-9</t>
         </is>
       </c>
-      <c r="U42" t="n">
+      <c r="W42" t="n">
         <v>18.62</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="X42" s="3" t="n">
         <v>-18.88</v>
       </c>
-      <c r="W42" t="n">
+      <c r="Y42" t="n">
         <v>1.12</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Z42" t="n">
         <v>53.99</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AA42" t="n">
         <v>148</v>
       </c>
-      <c r="Z42" t="b">
+      <c r="AB42" t="b">
         <v>1</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AC42" t="n">
         <v>160</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AD42" t="n">
         <v>11674</v>
       </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="inlineStr">
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
         <is>
           <t>Same five-clover pave-CZ station bracelet style (Chinese title: full-diamond five-flower clover), listed as 925 silver not 14K gold-plated alloy; single variant, metal tone unconfirmed, cost high vs Kalo price.</t>
         </is>
@@ -5719,71 +5996,76 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
           <t>British-style Double-breasted Long Wool Coat For Women</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>CJQB2587430</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/british-style-double-breasted-long-wool-coat-for-women-p-2511101334441610000.html</t>
         </is>
       </c>
-      <c r="O43" t="n">
+      <c r="Q43" t="n">
         <v>19.97</v>
       </c>
-      <c r="P43" t="n">
+      <c r="R43" t="n">
         <v>1700</v>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R43" t="n">
+      <c r="T43" t="n">
         <v>28.65</v>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U43" t="n">
+      <c r="W43" t="n">
         <v>48.62</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="X43" s="3" t="n">
         <v>-20.24</v>
       </c>
-      <c r="W43" t="n">
+      <c r="Y43" t="n">
         <v>-0.24</v>
       </c>
-      <c r="X43" t="n">
+      <c r="Z43" t="n">
         <v>85.99000000000001</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="AA43" t="n">
         <v>63</v>
       </c>
-      <c r="Z43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
+      <c r="AB43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
         <v>46</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AD43" t="n">
         <v>162663</v>
       </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="inlineStr">
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
         <is>
           <t>Same long double-breasted notched-lapel wool-blend coat in black and 6 other colours, but only XS-L Asian sizing (no XL) and heavy 1.7 kg so freight is high.</t>
         </is>
@@ -5839,71 +6121,76 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
           <t>Platform Chunky-heel Mary Jane Shoes</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>CJNS3060689</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/platform-chunky-heel-mary-jane-shoes-p-2608140641161612600.html</t>
         </is>
       </c>
-      <c r="O44" t="n">
+      <c r="Q44" t="n">
         <v>18.15</v>
       </c>
-      <c r="P44" t="n">
+      <c r="R44" t="n">
         <v>850</v>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R44" t="n">
+      <c r="T44" t="n">
         <v>15.73</v>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U44" t="n">
+      <c r="W44" t="n">
         <v>33.88</v>
       </c>
-      <c r="V44" s="3" t="n">
+      <c r="X44" s="3" t="n">
         <v>-21.84</v>
       </c>
-      <c r="W44" t="n">
+      <c r="Y44" t="n">
         <v>-1.84</v>
       </c>
-      <c r="X44" t="n">
+      <c r="Z44" t="n">
         <v>69.99000000000001</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AA44" t="n">
         <v>99</v>
       </c>
-      <c r="Z44" t="b">
+      <c r="AB44" t="b">
         <v>1</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AC44" t="n">
         <v>4</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AD44" t="n">
         <v>258834</v>
       </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="inlineStr">
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
         <is>
           <t>Same platform round-toe block-heel Mary Jane with buckle strap; heel listed 6-8 cm (a bit taller than 'low'), microfiber upper; new listing (4 listed).</t>
         </is>
@@ -5959,71 +6246,76 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
           <t>Versatile Button-fly Straight-leg Trousers</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>CJTZ2640367</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/versatile-button-fly-straight-leg-trousers-p-2512110959361603500.html</t>
         </is>
       </c>
-      <c r="O45" t="n">
+      <c r="Q45" t="n">
         <v>5.95</v>
       </c>
-      <c r="P45" t="n">
+      <c r="R45" t="n">
         <v>460</v>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R45" t="n">
+      <c r="T45" t="n">
         <v>10.71</v>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U45" t="n">
+      <c r="W45" t="n">
         <v>16.66</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="X45" s="3" t="n">
         <v>-22.18</v>
       </c>
-      <c r="W45" t="n">
+      <c r="Y45" t="n">
         <v>-2.18</v>
       </c>
-      <c r="X45" t="n">
+      <c r="Z45" t="n">
         <v>50.99</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="AA45" t="n">
         <v>218</v>
       </c>
-      <c r="Z45" t="b">
+      <c r="AB45" t="b">
         <v>1</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AC45" t="n">
         <v>4</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AD45" t="n">
         <v>28259</v>
       </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="inlineStr">
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
         <is>
           <t>Button-fly straight-leg trousers, but only one colour (dark blue, likely denim-look) and straight rather than slim-fit; the closer slim button trouser (CJNSXZKT00592) is green-only S-L.</t>
         </is>
@@ -6079,82 +6371,87 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
           <t>High Stretch Mid-Rise Barrel Jeans Fashion Wide Leg Shape Women Casual Baggy Mid Waist Denim Jeans</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>CJNZ1957871</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/high-stretch-mid-rise-barrel-jeans-fashion-wide-leg-shape-women-casual-baggy-mid-waist-denim-jeans-p-1751080947300175872.html</t>
         </is>
       </c>
-      <c r="O46" t="n">
+      <c r="Q46" t="n">
         <v>13.87</v>
       </c>
-      <c r="P46" t="n">
+      <c r="R46" t="n">
         <v>848</v>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R46" t="n">
+      <c r="T46" t="n">
         <v>15.69</v>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U46" t="n">
+      <c r="W46" t="n">
         <v>29.56</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="X46" s="3" t="n">
         <v>-22.6</v>
       </c>
-      <c r="W46" t="n">
+      <c r="Y46" t="n">
         <v>-2.6</v>
       </c>
-      <c r="X46" t="n">
+      <c r="Z46" t="n">
         <v>65.99000000000001</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="AA46" t="n">
         <v>123</v>
       </c>
-      <c r="Z46" t="b">
+      <c r="AB46" t="b">
         <v>1</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AC46" t="n">
         <v>754</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AD46" t="n">
         <v>634262</v>
       </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
         <v>6</v>
       </c>
-      <c r="AE46" t="n">
+      <c r="AG46" t="n">
         <v>4.5</v>
       </c>
-      <c r="AF46" t="inlineStr">
+      <c r="AH46" t="inlineStr">
         <is>
           <t>Looks like the photos, comfy, good fit; one says zip fly feels fragile.</t>
         </is>
       </c>
-      <c r="AG46" t="inlineStr">
+      <c r="AI46" t="inlineStr">
         <is>
           <t>Mid-rise baggy barrel/wide-leg denim in many washes; not distressed, and CJ description says polyester and 'inelastic' despite 'High Stretch' title.</t>
         </is>
@@ -6210,74 +6507,79 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
           <t>Butterfly Big Hoop Earring Full Cubic Zircon Circle Earrings For Women Girls Rhinestone Round Earring Jewelry Good Gift</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>CJLX1152553</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/butterfly-big-hoop-earring-full-cubic-zircon-circle-earrings-for-women-girls-rhinestone-round-earring-jewelry-good-gift-p-1399247909626712064.html</t>
         </is>
       </c>
-      <c r="O47" t="n">
+      <c r="Q47" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="P47" t="n">
+      <c r="R47" t="n">
         <v>36</v>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R47" t="n">
+      <c r="T47" t="n">
         <v>5.01</v>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>CJPacket Pure Electricity</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>7-14</t>
         </is>
       </c>
-      <c r="U47" t="n">
+      <c r="W47" t="n">
         <v>14.21</v>
       </c>
-      <c r="V47" s="3" t="n">
+      <c r="X47" s="3" t="n">
         <v>-23.11</v>
       </c>
-      <c r="W47" t="n">
+      <c r="Y47" t="n">
         <v>-3.11</v>
       </c>
-      <c r="X47" t="n">
+      <c r="Z47" t="n">
         <v>48.99</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="AA47" t="n">
         <v>296</v>
       </c>
-      <c r="Z47" t="b">
+      <c r="AB47" t="b">
         <v>1</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AC47" t="n">
         <v>50</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AD47" t="n">
         <v>109470</v>
       </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="inlineStr">
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
         <is>
           <t>Big full-CZ butterfly hoop earrings (golden or multicolour) with no heart element, more statement than the dainty butterfly-and-heart hoops; the cheap $1.69 variant is a different stud.</t>
         </is>
@@ -6333,71 +6635,76 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
           <t>Pointed Buckle Pleated Pile Style Boots Punk Mid Heel Knee-high Boots</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>CJNS2197810</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/pointed-buckle-pleated-pile-style-boots-punk-mid-heel-knee-high-boots-p-2411160907311629100.html</t>
         </is>
       </c>
-      <c r="O48" t="n">
+      <c r="Q48" t="n">
         <v>19.73</v>
       </c>
-      <c r="P48" t="n">
+      <c r="R48" t="n">
         <v>1550</v>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R48" t="n">
+      <c r="T48" t="n">
         <v>26.36</v>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="U48" t="n">
+      <c r="W48" t="n">
         <v>46.09</v>
       </c>
-      <c r="V48" s="3" t="n">
+      <c r="X48" s="3" t="n">
         <v>-37.42</v>
       </c>
-      <c r="W48" t="n">
+      <c r="Y48" t="n">
         <v>-17.42</v>
       </c>
-      <c r="X48" t="n">
+      <c r="Z48" t="n">
         <v>82.99000000000001</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="AA48" t="n">
         <v>164</v>
       </c>
-      <c r="Z48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
+      <c r="AB48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
         <v>40</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AD48" t="n">
         <v>192581</v>
       </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="inlineStr">
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
         <is>
           <t>Slouchy pleated PU knee-high with buckle strap, but pointed toe and ~5cm mid heel vs round-toe low-heel moto; sizes only EU 35-39; 1.5 kg makes freight ~$26.</t>
         </is>
@@ -6453,59 +6760,64 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
           <t>Outdoor Summer Women Men Sandals Beach Slippers Garden Clogs Shoes</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>CJNS1689490</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/outdoor-summer-women-men-sandals-beach-slippers-garden-clogs-shoes-p-1627934133861634048.html</t>
         </is>
       </c>
-      <c r="O49" t="n">
+      <c r="Q49" t="n">
         <v>2.53</v>
       </c>
-      <c r="P49" t="n">
+      <c r="R49" t="n">
         <v>360</v>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R49" t="n">
+      <c r="T49" t="n">
         <v>9.19</v>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="Z49" t="b">
+      <c r="AB49" t="b">
         <v>1</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AC49" t="n">
         <v>905</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AD49" t="n">
         <v>160911</v>
       </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="inlineStr">
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
         <is>
           <t>Plain EVA classic garden clog lookalike (black/white/pink); no metallic finish or metal buckle found on CJ, so the metallic ad angle is lost; double sizes (e.g. 38-39).</t>
         </is>
@@ -6561,59 +6873,64 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
           <t>Chunky Heel Platform Small Leather Slip-on Loafers</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>CJNS1468135</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/chunky-heel-platform-small-leather-slip-on-loafers-p-1517010683530063872.html</t>
         </is>
       </c>
-      <c r="O50" t="n">
+      <c r="Q50" t="n">
         <v>6.26</v>
       </c>
-      <c r="P50" t="n">
+      <c r="R50" t="n">
         <v>750</v>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R50" t="n">
+      <c r="T50" t="n">
         <v>14.2</v>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="Z50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
+      <c r="AB50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
         <v>43</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AD50" t="n">
         <v>266615</v>
       </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="inlineStr">
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
         <is>
           <t>Generic PU leather chunky-heel platform slip-on loafer, not a molded foam clog; loses the Crocs brand, material and comfort angle; EU 35-40 only (no US 10).</t>
         </is>
@@ -6669,74 +6986,79 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
+          <t>not checked</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
           <t>Fox Ears Warm With Velvet Knitted Plush Bonnet</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>CJBQ1810291</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>https://www.cjdropshipping.com/product/fox-ears-warm-with-velvet-knitted-plush-bonnet-p-1685155090291757056.html</t>
         </is>
       </c>
-      <c r="O51" t="n">
+      <c r="Q51" t="n">
         <v>2.81</v>
       </c>
-      <c r="P51" t="n">
+      <c r="R51" t="n">
         <v>240</v>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="R51" t="n">
+      <c r="T51" t="n">
         <v>7.36</v>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>LuWei Ordinary US</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>5-11</t>
         </is>
       </c>
-      <c r="Z51" t="b">
+      <c r="AB51" t="b">
         <v>1</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AC51" t="n">
         <v>12</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AD51" t="n">
         <v>79737</v>
       </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
         <v>10</v>
       </c>
-      <c r="AE51" t="n">
+      <c r="AG51" t="n">
         <v>4.6</v>
       </c>
-      <c r="AF51" t="inlineStr">
+      <c r="AH51" t="inlineStr">
         <is>
           <t>Warm, matches description; six identical templated 5-star reviews; one non-delivery.</t>
         </is>
       </c>
-      <c r="AG51" t="inlineStr">
+      <c r="AI51" t="inlineStr">
         <is>
           <t>Fox-ear plush velvet knit winter hat (6 colours), not a satin-lined sleep bonnet with an adjustable band; same cute fox-ear look but a different use and no anti-frizz angle.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG51"/>
+  <autoFilter ref="A1:AI51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6847,7 +7169,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Matches were judged from CJ titles and variants, not photos. Check photos before listing anything.</t>
+          <t>match was judged from CJ titles and variants. photo_verdict (match / partial / no) compares the TikTok and CJ main photos side by side; only the 12 picks within 20% of the TikTok price were checked.</t>
         </is>
       </c>
     </row>

--- a/data/kalo_cj/picking_sheet_2026-10-29.xlsx
+++ b/data/kalo_cj/picking_sheet_2026-10-29.xlsx
@@ -652,44 +652,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Shoes</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Clarks Collection Loafers -Westlynn Ayla</t>
+          <t>The Barb Wire Choker Danielle Guizio X The M Jewelers Necklace</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>204227.68</v>
+        <v>87038.5</v>
       </c>
       <c r="F2" t="n">
-        <v>3112</v>
+        <v>1238</v>
       </c>
       <c r="G2" t="n">
-        <v>65.63</v>
+        <v>70.31</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>97.41</t>
+          <t>-10.01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>QVC, Inc</t>
+          <t>themjewelersny</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/view/product/1731966485847774151?region=US</t>
+          <t>https://www.tiktok.com/view/product/1732377057880544126?region=US</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -699,34 +699,34 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Same chunky lug-sole penny loafer shape in black and brown; CJ has a metal bit instead of the croc-embossed strap.</t>
+          <t>Re-matched: CJLX1504225 thin barbed-wire choker, same shape as the winner but silver not gold. Photo tag reads ORNAMENTUS (possible other brand): sample first, don't reuse that photo.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Women Classic Elegant Fashion 2026 New Round Toe Block Low Heel Loafer Leather Shoes Elegant Versatile Pumps</t>
+          <t>Barbed Wire Necklace</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>CJNS3043308</t>
+          <t>CJLX1504225</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://www.cjdropshipping.com/product/women-classic-elegant-fashion-2026-new-round-toe-block-low-heel-loafer-leather-shoes-elegant-versatile-pumps-p-2085598370886311938.html</t>
+          <t>https://www.cjdropshipping.com/product/barbed-wire-necklace-p-1537624790973034496.html</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>6.6</v>
+        <v>6.29</v>
       </c>
       <c r="R2" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -734,11 +734,11 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>11.32</v>
+        <v>4.82</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>LuWei Ordinary US</t>
+          <t>CJPacket Super Pure Electricity</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -747,82 +747,79 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>17.92</v>
+        <v>11.11</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>22.23</v>
+        <v>33.35</v>
       </c>
       <c r="Y2" t="n">
-        <v>42.23</v>
+        <v>53.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>52.99</v>
+        <v>44.99</v>
       </c>
       <c r="AA2" t="n">
-        <v>-19</v>
+        <v>-36</v>
       </c>
       <c r="AB2" t="b">
         <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="AD2" t="n">
-        <v>103466</v>
+        <v>95350</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Generic round-toe low block-heel loafer in black/brown PU, unbranded lookalike of the Clarks heeled loafer (no Clarks leather or cushioning); low listedNum (5).</t>
+          <t>Re-matched after photo check: thin barbed-wire choker, same shape as the winner but silver only (no gold on CJ). Clasp tag in CJ photo reads ORNAMENTUS (another brand?): sample before listing.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C08</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Shoes</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>April Satin Pant</t>
+          <t>Clarks Collection Loafers -Westlynn Ayla</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>424640.14</v>
+        <v>204227.68</v>
       </c>
       <c r="F3" t="n">
-        <v>6921</v>
+        <v>3112</v>
       </c>
       <c r="G3" t="n">
-        <v>61.36</v>
+        <v>65.63</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>48.81</t>
+          <t>97.41</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>April Seven Studio</t>
+          <t>QVC, Inc</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/view/product/1731468041024738009?region=US</t>
+          <t>https://www.tiktok.com/view/product/1731966485847774151?region=US</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -837,29 +834,29 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Same high-waist satin wide-leg pant; CJ photo is pink but black is a variant. Fabric is acetate satin.</t>
+          <t>Same chunky lug-sole penny loafer shape in black and brown; CJ has a metal bit instead of the croc-embossed strap.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Casual Pants High Waist Acetate Satin Wide Leg Pants For Women</t>
+          <t>Women Classic Elegant Fashion 2026 New Round Toe Block Low Heel Loafer Leather Shoes Elegant Versatile Pumps</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>CJTZ1911661</t>
+          <t>CJNS3043308</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://www.cjdropshipping.com/product/casual-pants-high-waist-acetate-satin-wide-leg-pants-for-women-p-1731134489503469568.html</t>
+          <t>https://www.cjdropshipping.com/product/women-classic-elegant-fashion-2026-new-round-toe-block-low-heel-loafer-leather-shoes-elegant-versatile-pumps-p-2085598370886311938.html</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>9.449999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="R3" t="n">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -867,7 +864,7 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>9.5</v>
+        <v>11.32</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -880,28 +877,28 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>18.95</v>
+        <v>17.92</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>17.26</v>
+        <v>22.23</v>
       </c>
       <c r="Y3" t="n">
-        <v>37.26</v>
+        <v>42.23</v>
       </c>
       <c r="Z3" t="n">
-        <v>53.99</v>
+        <v>52.99</v>
       </c>
       <c r="AA3" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="AB3" t="b">
         <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="AD3" t="n">
-        <v>191156</v>
+        <v>103466</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -911,51 +908,51 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>High-waist acetate-look satin wide-leg pants in apricot/pink/black/gray; Kalodata title gives no detail, so exact cut and waistband may differ.</t>
+          <t>Generic round-toe low block-heel loafer in black/brown PU, unbranded lookalike of the Clarks heeled loafer (no Clarks leather or cushioning); low listedNum (5).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>C08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>WMP Eyewear Astra Cat-Eye Sunglasses for Women, Bold Modern Frame, Lightweight Trendy Sunglasses with UV Protection</t>
+          <t>April Satin Pant</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>196556.64</v>
+        <v>424640.14</v>
       </c>
       <c r="F4" t="n">
-        <v>4328</v>
+        <v>6921</v>
       </c>
       <c r="G4" t="n">
-        <v>45.42</v>
+        <v>61.36</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-39.88</t>
+          <t>48.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>WMP Eyewear</t>
+          <t>April Seven Studio</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/view/product/1732201295444087593?region=US</t>
+          <t>https://www.tiktok.com/view/product/1731468041024738009?region=US</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -965,34 +962,34 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>match</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Winner is a bold thick oval cat-eye; CJ is a thin half-rim mini cat-eye. Different look.</t>
+          <t>Same high-waist satin wide-leg pant; CJ photo is pink but black is a variant. Fabric is acetate satin.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Cat Eye Sunglasses Women European And American Fashion Trending</t>
+          <t>Casual Pants High Waist Acetate Satin Wide Leg Pants For Women</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>CJCF1968233</t>
+          <t>CJTZ1911661</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://www.cjdropshipping.com/product/cat-eye-sunglasses-women-european-and-american-fashion-trending-p-1757567002828349440.html</t>
+          <t>https://www.cjdropshipping.com/product/casual-pants-high-waist-acetate-satin-wide-leg-pants-for-women-p-1731134489503469568.html</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>1.65</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>40</v>
+        <v>380</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1000,7 +997,7 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>5.27</v>
+        <v>9.5</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1013,28 +1010,28 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>6.92</v>
+        <v>18.95</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>14.61</v>
+        <v>17.26</v>
       </c>
       <c r="Y4" t="n">
-        <v>34.61</v>
+        <v>37.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>40.99</v>
+        <v>53.99</v>
       </c>
       <c r="AA4" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="AB4" t="b">
         <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>357</v>
+        <v>78</v>
       </c>
       <c r="AD4" t="n">
-        <v>111129</v>
+        <v>191156</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -1044,51 +1041,51 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Generic plastic-frame trendy cat-eye sunglasses in 9 colourways; frame thickness vs the bold Astra and the UV rating are not stated on the listing.</t>
+          <t>High-waist acetate-look satin wide-leg pants in apricot/pink/black/gray; Kalodata title gives no detail, so exact cut and waistband may differ.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Comfrt | VIP Airplane Mode Travel Zip Hoodie - Mega | CloudTouch Fleece Zip-Up With Silk-Lined Hood &amp; Eye Mask</t>
+          <t>WMP Eyewear Astra Cat-Eye Sunglasses for Women, Bold Modern Frame, Lightweight Trendy Sunglasses with UV Protection</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>318470.2</v>
+        <v>196556.64</v>
       </c>
       <c r="F5" t="n">
-        <v>5091</v>
+        <v>4328</v>
       </c>
       <c r="G5" t="n">
-        <v>62.56</v>
+        <v>45.42</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>-39.88</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Comfrt</t>
+          <t>WMP Eyewear</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/view/product/1732607430962811779?region=US</t>
+          <t>https://www.tiktok.com/view/product/1732201295444087593?region=US</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1098,34 +1095,34 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Same eye-mask hood idea (the TikTok hook); CJ is a pullover not a zip-up and has no mega-fit claim.</t>
+          <t>Re-matched: CJCF1177466 thick cat-eye in brown tortoise; bold frame like the winner but a sharper cat-eye shape and lighter colour.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Eye-mask Hoodie 350g Fleece-lined Sweatshirt</t>
+          <t>Cat-eye Frame Sunglasses INS Style Sunglasses</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>CJWY2725041</t>
+          <t>CJCF1177466</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://www.cjdropshipping.com/product/eye-mask-hoodie-350g-fleece-lined-sweatshirt-p-2601110708231630100.html</t>
+          <t>https://www.cjdropshipping.com/product/cat-eye-frame-sunglasses-ins-style-sunglasses-p-1405348596290818048.html</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>13.43</v>
+        <v>1.46</v>
       </c>
       <c r="R5" t="n">
-        <v>410</v>
+        <v>40</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1133,7 +1130,7 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>9.949999999999999</v>
+        <v>5.27</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1146,82 +1143,79 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>23.38</v>
+        <v>6.73</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>13.94</v>
+        <v>14.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>33.94</v>
+        <v>34.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>58.99</v>
+        <v>40.99</v>
       </c>
       <c r="AA5" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="AB5" t="b">
         <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="AD5" t="n">
-        <v>119616</v>
+        <v>86361</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Fleece-lined hoodie with built-in eye-mask hood (same travel angle) in 4 colours; pullover not zip-up, no silk-lined hood, men's/unisex cut.</t>
+          <t>Re-matched after photo check: thick acetate-look cat-eye, brown (tortoise) variant; sharper cat-eye than the winner's soft oval. Also white and grey.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shoes</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Crocs Adult Classic Cozzzy Slippers, Fuzzy Slippers</t>
+          <t>Comfrt | VIP Airplane Mode Travel Zip Hoodie - Mega | CloudTouch Fleece Zip-Up With Silk-Lined Hood &amp; Eye Mask</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>558438.3</v>
+        <v>318470.2</v>
       </c>
       <c r="F6" t="n">
-        <v>11635</v>
+        <v>5091</v>
       </c>
       <c r="G6" t="n">
-        <v>48</v>
+        <v>62.56</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2042.92</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CROCS US SHOP</t>
+          <t>Comfrt</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/view/product/1730493404455474110?region=US</t>
+          <t>https://www.tiktok.com/view/product/1732607430962811779?region=US</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1231,34 +1225,34 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>match</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Winner is an all-fur slipper; CJ is a perforated garden clog with a fur cuff.</t>
+          <t>Same eye-mask hood idea (the TikTok hook); CJ is a pullover not a zip-up and has no mega-fit claim.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Fuzzy Plush Garden Clogs Mules Slippers Home Indoor Couple Slippers</t>
+          <t>Eye-mask Hoodie 350g Fleece-lined Sweatshirt</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>CJNS1050784</t>
+          <t>CJWY2725041</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://www.cjdropshipping.com/product/fuzzy-plush-garden-clogs-mules-slippers-home-indoor-couple-slippers-p-1373889976009363456.html</t>
+          <t>https://www.cjdropshipping.com/product/eye-mask-hoodie-350g-fleece-lined-sweatshirt-p-2601110708231630100.html</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>2.3</v>
+        <v>13.43</v>
       </c>
       <c r="R6" t="n">
-        <v>269</v>
+        <v>410</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1266,7 +1260,7 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>7.81</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1279,42 +1273,45 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>10.11</v>
+        <v>23.38</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>13.8</v>
+        <v>13.94</v>
       </c>
       <c r="Y6" t="n">
-        <v>33.8</v>
+        <v>33.94</v>
       </c>
       <c r="Z6" t="n">
-        <v>43.99</v>
+        <v>58.99</v>
       </c>
       <c r="AA6" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AB6" t="b">
         <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>543</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
-        <v>2000000</v>
+        <v>119616</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Unbranded plush-lined garden clog mule (closed toe, fuzzy lining) rather than Crocs Cozzzy open sandal-slipper; listed as men's/couple sizes 36-45.</t>
+          <t>Fleece-lined hoodie with built-in eye-mask hood (same travel angle) in 4 colours; pullover not zip-up, no silk-lined hood, men's/unisex cut.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1323,25 +1320,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Crocs Adult Unfurgettable Furry Lined Clogs, Fuzzy Slippers</t>
+          <t>Crocs Adult Classic Cozzzy Slippers, Fuzzy Slippers</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>238816.09</v>
+        <v>558438.3</v>
       </c>
       <c r="F7" t="n">
-        <v>5002</v>
+        <v>11635</v>
       </c>
       <c r="G7" t="n">
-        <v>47.74</v>
+        <v>48</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>2042.92</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1351,7 +1348,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/view/product/1732481650106799038?region=US</t>
+          <t>https://www.tiktok.com/view/product/1730493404455474110?region=US</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1366,7 +1363,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Winner is a fur-covered clog; CJ is a perforated garden clog with a fur cuff.</t>
+          <t>Winner is an all-fur slipper; CJ is a perforated garden clog with a fur cuff.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1412,10 +1409,10 @@
         <v>10.11</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>13.56</v>
+        <v>13.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>33.56</v>
+        <v>33.8</v>
       </c>
       <c r="Z7" t="n">
         <v>43.99</v>
@@ -1437,51 +1434,51 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Same CJ product as S01: unbranded EVA garden clog with plush lining; lacks the Crocs furry exterior and strap; no closer furry-lined clog found on CJ.</t>
+          <t>Unbranded plush-lined garden clog mule (closed toe, fuzzy lining) rather than Crocs Cozzzy open sandal-slipper; listed as men's/couple sizes 36-45.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>S07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Shoes</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The Barb Wire Choker Danielle Guizio X The M Jewelers Necklace</t>
+          <t>Crocs Adult Unfurgettable Furry Lined Clogs, Fuzzy Slippers</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>87038.5</v>
+        <v>238816.09</v>
       </c>
       <c r="F8" t="n">
-        <v>1238</v>
+        <v>5002</v>
       </c>
       <c r="G8" t="n">
-        <v>70.31</v>
+        <v>47.74</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-10.01</t>
+          <t>58.31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>themjewelersny</t>
+          <t>CROCS US SHOP</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/view/product/1732377057880544126?region=US</t>
+          <t>https://www.tiktok.com/view/product/1732481650106799038?region=US</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1491,34 +1488,34 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>no</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Barbed-wire idea matches but CJ is a chunky silver iced-out chain; the winner is a dainty gold choker. CJ cost $26.</t>
+          <t>Winner is a fur-covered clog; CJ is a perforated garden clog with a fur cuff.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2.5mm Wire Chain Hip Hop Necklace Micro Inlaid Sun Word Buckle Thorns</t>
+          <t>Fuzzy Plush Garden Clogs Mules Slippers Home Indoor Couple Slippers</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>CJLX1518256</t>
+          <t>CJNS1050784</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://www.cjdropshipping.com/product/2.5mm-wire-chain-hip-hop-necklace-micro-inlaid-sun-word-buckle-thorns-p-1544546445079498752.html</t>
+          <t>https://www.cjdropshipping.com/product/fuzzy-plush-garden-clogs-mules-slippers-home-indoor-couple-slippers-p-1373889976009363456.html</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>26.41</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>42</v>
+        <v>269</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1526,51 +1523,48 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>5.01</v>
+        <v>7.81</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>CJPacket Pure Electricity</t>
+          <t>LuWei Ordinary US</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>7-14</t>
+          <t>5-11</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>31.42</v>
+        <v>10.11</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>13.04</v>
+        <v>13.56</v>
       </c>
       <c r="Y8" t="n">
-        <v>33.04</v>
+        <v>33.56</v>
       </c>
       <c r="Z8" t="n">
-        <v>67.99000000000001</v>
+        <v>43.99</v>
       </c>
       <c r="AA8" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="AB8" t="b">
         <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>543</v>
       </c>
       <c r="AD8" t="n">
-        <v>192925</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Unbranded lookalike: thin 2.5mm micro-pave CZ barbed-wire chain on gold-plated copper (gold/white gold, 14-20in), not the Danielle Guizio x M Jewelers piece; cost is high for CJ.</t>
+          <t>Same CJ product as S01: unbranded EVA garden clog with plush lining; lacks the Crocs furry exterior and strap; no closer furry-lined clog found on CJ.</t>
         </is>
       </c>
     </row>
